--- a/data/Event_Data_NNB02VR-101.xlsx
+++ b/data/Event_Data_NNB02VR-101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-09-2569 11:27</t>
+          <t>16-10-2569 15:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,14 +468,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19-07-2569 06:49</t>
+          <t>11-09-2569 11:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,14 +490,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11-06-2569 00:09</t>
+          <t>19-07-2569 06:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -512,27 +512,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>11-06-2569 00:09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NNB02VR-101</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>27-11-2568 12:30</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>NNB02VR-101</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>T/L</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>T/L ไม่พบสาเหตุ จ่ายไฟ 13.38</t>
         </is>
